--- a/src/test/resources/test-data/LoginData.xlsx
+++ b/src/test/resources/test-data/LoginData.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Uok\Term8\QA\Automation\first\src\test\resources\test-data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Uok\Term8\QA\Automation\selenium-testng-framework\src\test\resources\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -511,7 +511,7 @@
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
